--- a/Target Folder/QA-Files/zh-CN/Test Data Sheet.xlsx
+++ b/Target Folder/QA-Files/zh-CN/Test Data Sheet.xlsx
@@ -13,9 +13,9 @@
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Testing 1" sheetId="1" r:id="rId1"/>
-    <sheet name="Testing 2" sheetId="2" r:id="rId2"/>
-    <sheet name="Testing 3" sheetId="3" r:id="rId3"/>
+    <sheet name="测试 1" sheetId="1" r:id="rId1"/>
+    <sheet name="测试 2" sheetId="2" r:id="rId2"/>
+    <sheet name="测试 3" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
@@ -26,109 +26,109 @@
   <si>
     <r>
       <rPr/>
-      <t>Source Text English (en-US)</t>
+      <t>源文本英语 (en-US)</t>
     </r>
   </si>
   <si>
     <r>
       <rPr/>
-      <t>Chinese</t>
+      <t>中文</t>
     </r>
   </si>
   <si>
     <r>
       <rPr/>
-      <t>Arabic</t>
+      <t>阿拉伯语</t>
     </r>
   </si>
   <si>
     <r>
       <rPr/>
-      <t>German</t>
+      <t>德语</t>
     </r>
   </si>
   <si>
     <r>
       <rPr/>
-      <t>Italian</t>
+      <t>意大利语</t>
     </r>
   </si>
   <si>
     <r>
       <rPr/>
-      <t>French</t>
+      <t>法语</t>
     </r>
   </si>
   <si>
     <r>
       <rPr/>
-      <t>I would like to drink before the urn, but it flatters the free will.Children's children in the lake of basketball.In fact, the fear of football is the makeup of the real estate.</t>
+      <t>我想在骨灰瓮前喝酒，但它迎合了自由意志。篮球湖中的孩子们。事实上，对足球的恐惧是房地产的构成。</t>
     </r>
   </si>
   <si>
     <r>
       <rPr/>
-      <t>Mauris mattis sem ex, not easy molestie sapien.The development of tincidunt urn at hate receives, or homework trigger course.Even the land is large, it is necessary and it takes in, the laoreet quis felis.Therefore, it is not necessary to treat this disease.</t>
+      <t>毛里求斯马蒂斯半前，不轻易打扰萨皮恩。对憎恨的锡西丁瓮的开发收到，或家庭作业触发课程。即使土地很大，也需要并且它包含，laoreet quis felis。因此，没有必要治疗这种疾病。</t>
     </r>
   </si>
   <si>
     <r>
       <rPr/>
-      <t>Vestibulum eleifend, ligula from chocolate vehicles, laughter just ultricies ligula, and sometimes lorem from eget ex.Duis dignissim lacus vitae velit laoreet, vitae investrat velit aliquet.</t>
+      <t>前庭电梯，来自巧克力车的韧带，只是大笑的韧带，有时来自前任的 lorem。Duis dignissim lacus vitae velit laoreet, vitae investrat velit aliquet。</t>
     </r>
   </si>
   <si>
     <r>
       <rPr/>
-      <t>I don't even need a soft drink, and my vehicles.I don't want to worry too much about financing.Find out who the country is.Until said Euismod smile not time.Who are the kids now?It's a soft sauce element.</t>
+      <t>我甚至不需要软饮料，和我的车。我不想过多担心融资问题。查明这个国家是谁。直到说Euismod微笑没有时间。现在的孩子们是谁？这是一种软酱元素。</t>
     </r>
   </si>
   <si>
     <r>
       <rPr/>
-      <t>The boat that the Hendrerit places.But basketball flatters none but the members.Now, who is the eros?It also flatters the drink.</t>
+      <t>亨德里特放置的船。但篮球只讨好成员。现在，谁是爱神？它也使饮料增色不少。</t>
     </r>
   </si>
   <si>
     <r>
       <rPr/>
-      <t>Curabitur lacinia cursus diam sed pharetra.It seems that the employee is sad.Until it was pure hatred, the employee accepted it, the airline was in it.I can't even carry a porta terrarium.Each price flatters the asset.</t>
+      <t>Curabitur lacinia cursus diam sed pharetra。看来这位员工很难过。直到纯粹的仇恨，员工接受了它，航空公司也身在其中。我甚至不能携带一个便携式生态箱。每个价格都使资产增值。</t>
     </r>
   </si>
   <si>
     <r>
       <rPr/>
-      <t>Because of this, the fear of the valley is made soft.现在，悲伤从此刻开始装饰，不再奉承宫廷的喉咙。Aenean是为我而饮，还是不为我而饮？</t>
+      <t>正因为如此，对山谷的恐惧变得柔和。现在，从今往后的哀悼装饰着，也不奉承法庭的喉舌。Aenean 为我喝酒或不喝 Euismod hendrerit。</t>
     </r>
   </si>
   <si>
     <r>
       <rPr/>
-      <t>一件圣袍和一个大箭袋。作为一种妆容，orci却奉承着喉咙，嘴唇上只有一丝微笑，就像ligula上暂时的欢声笑语。</t>
+      <t>一件祭服和一个大箭袋。作为一种妆容，orci 却奉承着喉咙，唇边只有一丝微笑，作为韧带处临时的笑声之床。</t>
     </r>
   </si>
   <si>
     <r>
       <rPr/>
-      <t>Duis不是纯粹的tincidunt。因为谁在欢笑中是明智的？直到山谷房地产的时间。</t>
+      <t>Duis 不是纯粹的 tincidunt。因为谁是笑声中的智者？直到山谷房地产的时代。</t>
     </r>
   </si>
   <si>
     <r>
       <rPr/>
-      <t>我不想买任何卡车，也不必支付床位的价格。它就像我的房地产经纪人一样讨人喜欢。</t>
+      <t>我不想买任何卡车，也不必支付床的价格。这就像我的房地产经纪人一样讨人喜欢。</t>
     </r>
   </si>
   <si>
     <r>
       <rPr/>
-      <t>为了成为一个成功的开发者，需要瞄准目标受众。大口喝酒很容易。在目标床上。</t>
+      <t>为了成为一名成功的开发者，需要锁定目标受众。散装饮用很容易。在目标床上。</t>
     </r>
   </si>
   <si>
     <r>
       <rPr/>
-      <t>In the quiet depths of the soul, a war is brewing—a silent battle fought in the landscapes of thought and emotion, where soldiers, memories, and fears gather at the edges, preparing for internal conflict.</t>
+      <t>在灵魂的宁静深处，一场战争正在酝酿——一场在思想和情感的景观中进行的无声战斗，士兵、记忆和恐惧聚集在边缘，为内部冲突做准备。</t>
     </r>
   </si>
   <si>
@@ -140,13 +140,13 @@
   <si>
     <r>
       <rPr/>
-      <t>However, the shadows of the past cast long, unsettling shades, the scars of lost battles appear as disturbing memories, each a ghostly reminder of wounds yet to heal.</t>
+      <t>然而，过去的阴影投下漫长而令人不安的阴影，失败战役的伤疤以令人不安的记忆形式出现，每一个都是尚未愈合的伤口的幽灵般的提醒。</t>
     </r>
   </si>
   <si>
     <r>
       <rPr/>
-      <t>In the fiery self-reflection, generals of ambition and procrastination strategize, with ambition in the armour of determination clashing with the elusive tactics of procrastination, leaving the battlefield of the mind in a state of perpetual uncertainty.</t>
+      <t>在炽热的自我反省中，野心和拖延症的将军们制定战略，决心盔甲中的野心与难以捉摸的拖延策略发生冲突，让心灵的战场处于一种永远不确定的状态。</t>
     </r>
   </si>
   <si>
@@ -194,25 +194,25 @@
   <si>
     <r>
       <rPr/>
-      <t>I would like to drink before the urn, but it flatters the free will.Children's children in the lake of basketball.In fact, the fear of football is the makeup of the real estate.Mauris mattis sem ex, not easy molestie sapien.The development of tincidunt urn at hate receives, or homework trigger course.Even the land is large, it is necessary and it takes in, the laoreet quis felis.Therefore, it is not necessary to treat this disease.</t>
+      <t>我想在骨灰瓮前喝酒，但它迎合了自由意志。篮球湖中的孩子们。事实上，对足球的恐惧是房地产的构成。毛里求斯马蒂斯半前，不轻易打扰萨皮恩。对憎恨的锡西丁瓮的开发收到，或家庭作业触发课程。即使土地很大，也需要并且它包含，laoreet quis felis。因此，没有必要治疗这种疾病。</t>
     </r>
   </si>
   <si>
     <r>
       <rPr/>
-      <t>Vestibulum eleifend, ligula from chocolate vehicles, laughter just ultricies ligula, and sometimes lorem from eget ex.Duis dignissim lacus vitae velit laoreet, vitae investrat velit aliquet.I don't even need a soft drink, and my vehicles.I don't want to worry too much about financing.Find out who the country is.Until said Euismod smile not time.Who are the kids now?It's a soft sauce element.</t>
+      <t>前庭电梯，来自巧克力车的韧带，只是大笑的韧带，有时来自前任的 lorem。Duis dignissim lacus vitae velit laoreet, vitae investrat velit aliquet。我甚至不需要软饮料，和我的车。我不想过多担心融资问题。查明这个国家是谁。直到说Euismod微笑没有时间。现在的孩子们是谁？这是一种软酱元素。</t>
     </r>
   </si>
   <si>
     <r>
       <rPr/>
-      <t>The boat that the Hendrerit places.But basketball flatters none but the members.Now, who is the eros?It also flatters the drink.Curabitur lacinia cursus diam sed pharetra.It seems that the employee is sad.Until it was pure hatred, the employee accepted it, the airline was in it.I can't even carry a porta terrarium.Each price flatters the asset.Because of this, the fear of the valley is made soft.现在，悲伤从此刻开始装饰，不再奉承宫廷的喉咙。Aenean是为我而饮，还是不为我而饮？一件圣袍和一个大箭袋。作为一种妆容，orci却奉承着喉咙，嘴唇上只有一丝微笑，就像ligula上暂时的欢声笑语。</t>
+      <t>亨德里特放置的船。但篮球只讨好成员。现在，谁是爱神？它也使饮料增色不少。Curabitur lacinia cursus diam sed pharetra。看来这位员工很难过。直到纯粹的仇恨，员工接受了它，航空公司也身在其中。我甚至不能携带一个便携式生态箱。每个价格都使资产增值。正因为如此，对山谷的恐惧变得柔和。现在，从今往后的哀悼装饰着，也不奉承法庭的喉舌。Aenean 为我喝酒或不喝 Euismod hendrerit。一件祭服和一个大箭袋。作为一种妆容，orci 却奉承着喉咙，唇边只有一丝微笑，作为韧带处临时的笑声之床。</t>
     </r>
   </si>
   <si>
     <r>
       <rPr/>
-      <t>Duis不是纯粹的tincidunt。因为谁在欢笑中是明智的？直到山谷房地产的时间。我不想买任何卡车，也不必支付床位的价格。它就像我的房地产经纪人一样讨人喜欢。为了成为一个成功的开发者，需要瞄准目标受众。大口喝酒很容易。在目标床上。</t>
+      <t>Duis 不是纯粹的 tincidunt。因为谁是笑声中的智者？直到山谷房地产的时代。我不想买任何卡车，也不必支付床的价格。这就像我的房地产经纪人一样讨人喜欢。为了成为一名成功的开发者，需要锁定目标受众。散装饮用很容易。在目标床上。</t>
     </r>
   </si>
   <si>
@@ -242,55 +242,55 @@
   <si>
     <r>
       <rPr/>
-      <t>通过提供这个必要的工具，我们可以确保新团队成员。</t>
+      <t>通过提供这一重要工具，我们可以确保新团队成员。</t>
     </r>
   </si>
   <si>
     <r>
       <rPr/>
-      <t>从一开始就能充分为我们项目的成功做出贡献。</t>
+      <t>能够从一开始就为我们项目的成功做出充分贡献。</t>
     </r>
   </si>
   <si>
     <r>
       <rPr/>
-      <t>这项对他们工作空间的投资不仅会提高他们的效率。</t>
+      <t>这项对其工作空间的投资不仅能提高他们的效率。</t>
     </r>
   </si>
   <si>
     <r>
       <rPr/>
-      <t>也体现了我们致力于为团队提供必要资源，以使其在各自岗位上表现卓越的承诺。</t>
+      <t>也体现了我们致力于为团队提供必要资源，使其在各自岗位上表现出色。</t>
     </r>
   </si>
   <si>
     <r>
       <rPr/>
-      <t>在随后的寂静中，心灵变成了一片被改造的战场——一片被内心战争所创伤的景观，内部斗争的回声萦绕不绝，证明了人类精神在驾驭复杂心灵地形时的韧性。</t>
+      <t>在随后的寂静中，思想变成了一个战场——一个被内心战争所创伤的景观，内部斗争的回响挥之不去，证明了人类精神在驾驭复杂思想领域的韧性。</t>
     </r>
   </si>
   <si>
     <r>
       <rPr/>
-      <t>只斜体标题，不斜体名称（例如，书名而不是船名）</t>
+      <t>仅斜体显示标题，而不是名称（例如，书名而非船名）</t>
     </r>
   </si>
   <si>
     <r>
       <rPr/>
-      <t>巴基斯坦是一个拥有超过2.4亿人口的国家，其经济是一幅复杂的画卷，由农业、工业、服务业和非正式经济部门等多元化的线索编织而成，后者虽然举足轻重却常被忽视。</t>
+      <t>巴基斯坦是一个拥有超过 2.4 亿人口的国家，其经济是一幅由农业、工业、服务业以及一个关键但经常被忽视的非正规部门等不同线索编织而成的复杂画卷。</t>
     </r>
   </si>
   <si>
     <r>
       <rPr/>
-      <t>截至2024年，巴基斯坦正处于一个关键时刻，它正努力应对挑战并探索机遇，这些挑战和机遇共同定义了其经济格局。</t>
+      <t>截至 2024 年，巴基斯坦正处于一个关键时刻，努力应对挑战并探索定义其经济格局的机遇。</t>
     </r>
   </si>
   <si>
     <r>
       <rPr/>
-      <t>Test Example</t>
+      <t>测试示例</t>
     </r>
   </si>
   <si>
@@ -302,7 +302,7 @@
   <si>
     <r>
       <rPr/>
-      <t>In the quiet depths of the soul, a war is brewing—a silent battle fought in the landscapes of thought and emotion, where soldiers, memories, and fears gather at the edges, preparing for internal conflict.</t>
+      <t>在灵魂的宁静深处，一场战争正在酝酿——一场在思想和情感的景观中进行的无声战斗，士兵、记忆和恐惧聚集在边缘，为内部冲突做准备。</t>
     </r>
   </si>
   <si>
@@ -314,13 +314,13 @@
   <si>
     <r>
       <rPr/>
-      <t>Test Example</t>
+      <t>测试示例</t>
     </r>
   </si>
   <si>
     <r>
       <rPr/>
-      <t>However, the shadows of the past cast long, unsettling shades, the scars of lost battles appear as disturbing memories, each a ghostly reminder of wounds yet to heal.</t>
+      <t>然而，过去的阴影投下漫长而令人不安的阴影，失败战役的伤疤以令人不安的记忆形式出现，每一个都是尚未愈合的伤口的幽灵般的提醒。</t>
     </r>
   </si>
   <si>
@@ -332,7 +332,7 @@
   <si>
     <r>
       <rPr/>
-      <t>In the fiery self-reflection, generals of ambition and procrastination strategize, with ambition in the armour of determination clashing with the elusive tactics of procrastination, leaving the battlefield of the mind in a state of perpetual uncertainty.</t>
+      <t>在炽热的自我反省中，野心和拖延症的将军们制定战略，决心盔甲中的野心与难以捉摸的拖延策略发生冲突，让心灵的战场处于一种永远不确定的状态。</t>
     </r>
   </si>
   <si>
@@ -380,127 +380,127 @@
   <si>
     <r>
       <rPr/>
-      <t>Source Text English (en-US)</t>
+      <t>源文本英语 (en-US)</t>
     </r>
   </si>
   <si>
     <r>
       <rPr/>
-      <t>Chinese</t>
+      <t>中文</t>
     </r>
   </si>
   <si>
     <r>
       <rPr/>
-      <t>Arabic</t>
+      <t>阿拉伯语</t>
     </r>
   </si>
   <si>
     <r>
       <rPr/>
-      <t>German</t>
+      <t>德语</t>
     </r>
   </si>
   <si>
     <r>
       <rPr/>
-      <t>Italian</t>
+      <t>意大利语</t>
     </r>
   </si>
   <si>
     <r>
       <rPr/>
-      <t>French</t>
+      <t>法语</t>
     </r>
   </si>
   <si>
     <r>
       <rPr/>
-      <t>I would like to drink before the urn, but it flatters the free will.Children's children in the lake of basketball.In fact, the fear of football is the makeup of the real estate.</t>
+      <t>我想在骨灰瓮前喝酒，但它迎合了自由意志。篮球湖中的孩子们。事实上，对足球的恐惧是房地产的构成。</t>
     </r>
   </si>
   <si>
     <r>
       <rPr/>
-      <t>Mauris mattis sem ex, not easy molestie sapien.The development of tincidunt urn at hate receives, or homework trigger course.Even the land is large, it is necessary and it takes in, the laoreet quis felis.Therefore, it is not necessary to treat this disease.</t>
+      <t>毛里求斯马蒂斯半前，不轻易打扰萨皮恩。对憎恨的锡西丁瓮的开发收到，或家庭作业触发课程。即使土地很大，也需要并且它包含，laoreet quis felis。因此，没有必要治疗这种疾病。</t>
     </r>
   </si>
   <si>
     <r>
       <rPr/>
-      <t>Vestibulum eleifend, ligula from chocolate vehicles, laughter just ultricies ligula, and sometimes lorem from eget ex.Duis dignissim lacus vitae velit laoreet, vitae investrat velit aliquet.</t>
+      <t>前庭电梯，来自巧克力车的韧带，只是大笑的韧带，有时来自前任的 lorem。Duis dignissim lacus vitae velit laoreet, vitae investrat velit aliquet。</t>
     </r>
   </si>
   <si>
     <r>
       <rPr/>
-      <t>I don't even need a soft drink, and my vehicles.I don't want to worry too much about financing.Find out who the country is.Until said Euismod smile not time.Who are the kids now?It's a soft sauce element.</t>
+      <t>我甚至不需要软饮料，和我的车。我不想过多担心融资问题。查明这个国家是谁。直到说Euismod微笑没有时间。现在的孩子们是谁？这是一种软酱元素。</t>
     </r>
   </si>
   <si>
     <r>
       <rPr/>
-      <t>The boat that the Hendrerit places.But basketball flatters none but the members.Now, who is the eros?It also flatters the drink.</t>
+      <t>亨德里特放置的船。但篮球只讨好成员。现在，谁是爱神？它也使饮料增色不少。</t>
     </r>
   </si>
   <si>
     <r>
       <rPr/>
-      <t>Curabitur lacinia cursus diam sed pharetra.It seems that the employee is sad.Until it was pure hatred, the employee accepted it, the airline was in it.I can't even carry a porta terrarium.Each price flatters the asset.</t>
+      <t>Curabitur lacinia cursus diam sed pharetra。看来这位员工很难过。直到纯粹的仇恨，员工接受了它，航空公司也身在其中。我甚至不能携带一个便携式生态箱。每个价格都使资产增值。</t>
     </r>
   </si>
   <si>
     <r>
       <rPr/>
-      <t>Because of this, the fear of the valley is made soft.现在，悲伤从此刻开始装饰，不再奉承宫廷的喉咙。Aenean是为我而饮，还是不为我而饮？</t>
+      <t>正因为如此，对山谷的恐惧变得柔和。现在，从今往后的哀悼装饰着，也不奉承法庭的喉舌。Aenean 为我喝酒或不喝 Euismod hendrerit。</t>
     </r>
   </si>
   <si>
     <r>
       <rPr/>
-      <t>一件圣袍和一个大箭袋。作为一种妆容，orci却奉承着喉咙，嘴唇上只有一丝微笑，就像ligula上暂时的欢声笑语。</t>
+      <t>一件祭服和一个大箭袋。作为一种妆容，orci 却奉承着喉咙，唇边只有一丝微笑，作为韧带处临时的笑声之床。</t>
     </r>
   </si>
   <si>
     <r>
       <rPr/>
-      <t>Duis不是纯粹的tincidunt。因为谁在欢笑中是明智的？直到山谷房地产的时间。</t>
+      <t>Duis 不是纯粹的 tincidunt。因为谁是笑声中的智者？直到山谷房地产的时代。</t>
     </r>
   </si>
   <si>
     <r>
       <rPr/>
-      <t>我不想买任何卡车，也不必支付床位的价格。它就像我的房地产经纪人一样讨人喜欢。</t>
+      <t>我不想买任何卡车，也不必支付床的价格。这就像我的房地产经纪人一样讨人喜欢。</t>
     </r>
   </si>
   <si>
     <r>
       <rPr/>
-      <t>为了成为一个成功的开发者，需要瞄准目标受众。大口喝酒很容易。在目标床上。</t>
+      <t>为了成为一名成功的开发者，需要锁定目标受众。散装饮用很容易。在目标床上。</t>
     </r>
   </si>
   <si>
     <r>
       <rPr/>
-      <t>I would like to drink before the urn, but it flatters the free will.Children's children in the lake of basketball.In fact, the fear of football is the makeup of the real estate.Mauris mattis sem ex, not easy molestie sapien.The development of tincidunt urn at hate receives, or homework trigger course.Even the land is large, it is necessary and it takes in, the laoreet quis felis.Therefore, it is not necessary to treat this disease.</t>
+      <t>我想在骨灰瓮前喝酒，但它迎合了自由意志。篮球湖中的孩子们。事实上，对足球的恐惧是房地产的构成。毛里求斯马蒂斯半前，不轻易打扰萨皮恩。对憎恨的锡西丁瓮的开发收到，或家庭作业触发课程。即使土地很大，也需要并且它包含，laoreet quis felis。因此，没有必要治疗这种疾病。</t>
     </r>
   </si>
   <si>
     <r>
       <rPr/>
-      <t>Vestibulum eleifend, ligula from chocolate vehicles, laughter just ultricies ligula, and sometimes lorem from eget ex.Duis dignissim lacus vitae velit laoreet, vitae investrat velit aliquet.I don't even need a soft drink, and my vehicles.I don't want to worry too much about financing.Find out who the country is.Until said Euismod smile not time.Who are the kids now?It's a soft sauce element.</t>
+      <t>前庭电梯，来自巧克力车的韧带，只是大笑的韧带，有时来自前任的 lorem。Duis dignissim lacus vitae velit laoreet, vitae investrat velit aliquet。我甚至不需要软饮料，和我的车。我不想过多担心融资问题。查明这个国家是谁。直到说Euismod微笑没有时间。现在的孩子们是谁？这是一种软酱元素。</t>
     </r>
   </si>
   <si>
     <r>
       <rPr/>
-      <t>The boat that the Hendrerit places.But basketball flatters none but the members.Now, who is the eros?It also flatters the drink.Curabitur lacinia cursus diam sed pharetra.It seems that the employee is sad.Until it was pure hatred, the employee accepted it, the airline was in it.I can't even carry a porta terrarium.Each price flatters the asset.Because of this, the fear of the valley is made soft.现在，悲伤从此刻开始装饰，不再奉承宫廷的喉咙。Aenean是为我而饮，还是不为我而饮？一件圣袍和一个大箭袋。作为一种妆容，orci却奉承着喉咙，嘴唇上只有一丝微笑，就像ligula上暂时的欢声笑语。</t>
+      <t>亨德里特放置的船。但篮球只讨好成员。现在，谁是爱神？它也使饮料增色不少。Curabitur lacinia cursus diam sed pharetra。看来这位员工很难过。直到纯粹的仇恨，员工接受了它，航空公司也身在其中。我甚至不能携带一个便携式生态箱。每个价格都使资产增值。正因为如此，对山谷的恐惧变得柔和。现在，从今往后的哀悼装饰着，也不奉承法庭的喉舌。Aenean 为我喝酒或不喝 Euismod hendrerit。一件祭服和一个大箭袋。作为一种妆容，orci 却奉承着喉咙，唇边只有一丝微笑，作为韧带处临时的笑声之床。</t>
     </r>
   </si>
   <si>
     <r>
       <rPr/>
-      <t>Duis不是纯粹的tincidunt。因为谁在欢笑中是明智的？直到山谷房地产的时间。我不想买任何卡车，也不必支付床位的价格。它就像我的房地产经纪人一样讨人喜欢。为了成为一个成功的开发者，需要瞄准目标受众。大口喝酒很容易。在目标床上。</t>
+      <t>Duis 不是纯粹的 tincidunt。因为谁是笑声中的智者？直到山谷房地产的时代。我不想买任何卡车，也不必支付床的价格。这就像我的房地产经纪人一样讨人喜欢。为了成为一名成功的开发者，需要锁定目标受众。散装饮用很容易。在目标床上。</t>
     </r>
   </si>
   <si>
@@ -530,49 +530,49 @@
   <si>
     <r>
       <rPr/>
-      <t>通过提供这个必要的工具，我们可以确保新团队成员。</t>
+      <t>通过提供这一重要工具，我们可以确保新团队成员。</t>
     </r>
   </si>
   <si>
     <r>
       <rPr/>
-      <t>从一开始就能充分为我们项目的成功做出贡献。</t>
+      <t>能够从一开始就为我们项目的成功做出充分贡献。</t>
     </r>
   </si>
   <si>
     <r>
       <rPr/>
-      <t>这项对他们工作空间的投资不仅会提高他们的效率。</t>
+      <t>这项对其工作空间的投资不仅能提高他们的效率。</t>
     </r>
   </si>
   <si>
     <r>
       <rPr/>
-      <t>也体现了我们致力于为团队提供必要资源，以使其在各自岗位上表现卓越的承诺。</t>
+      <t>也体现了我们致力于为团队提供必要资源，使其在各自岗位上表现出色。</t>
     </r>
   </si>
   <si>
     <r>
       <rPr/>
-      <t>在随后的寂静中，心灵变成了一片被改造的战场——一片被内心战争所创伤的景观，内部斗争的回声萦绕不绝，证明了人类精神在驾驭复杂心灵地形时的韧性。</t>
+      <t>在随后的寂静中，思想变成了一个战场——一个被内心战争所创伤的景观，内部斗争的回响挥之不去，证明了人类精神在驾驭复杂思想领域的韧性。</t>
     </r>
   </si>
   <si>
     <r>
       <rPr/>
-      <t>只斜体标题，不斜体名称（例如，书名而不是船名）</t>
+      <t>仅斜体显示标题，而不是名称（例如，书名而非船名）</t>
     </r>
   </si>
   <si>
     <r>
       <rPr/>
-      <t>巴基斯坦是一个拥有超过2.4亿人口的国家，其经济是一幅复杂的画卷，由农业、工业、服务业和非正式经济部门等多元化的线索编织而成，后者虽然举足轻重却常被忽视。</t>
+      <t>巴基斯坦是一个拥有超过 2.4 亿人口的国家，其经济是一幅由农业、工业、服务业以及一个关键但经常被忽视的非正规部门等不同线索编织而成的复杂画卷。</t>
     </r>
   </si>
   <si>
     <r>
       <rPr/>
-      <t>截至2024年，巴基斯坦正处于一个关键时刻，它正努力应对挑战并探索机遇，这些挑战和机遇共同定义了其经济格局。</t>
+      <t>截至 2024 年，巴基斯坦正处于一个关键时刻，努力应对挑战并探索定义其经济格局的机遇。</t>
     </r>
   </si>
 </sst>
